--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21877,6 +21877,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B936" t="n">
+        <v>0</v>
+      </c>
+      <c r="C936" t="n">
+        <v>4</v>
+      </c>
+      <c r="D936" t="n">
+        <v>4</v>
+      </c>
+      <c r="E936" t="n">
+        <v>4</v>
+      </c>
+      <c r="F936" t="n">
+        <v>4</v>
+      </c>
+      <c r="G936" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21900,6 +21900,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B937" t="n">
+        <v>0</v>
+      </c>
+      <c r="C937" t="n">
+        <v>4</v>
+      </c>
+      <c r="D937" t="n">
+        <v>4</v>
+      </c>
+      <c r="E937" t="n">
+        <v>4</v>
+      </c>
+      <c r="F937" t="n">
+        <v>4</v>
+      </c>
+      <c r="G937" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21923,6 +21923,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B938" t="n">
+        <v>0</v>
+      </c>
+      <c r="C938" t="n">
+        <v>4</v>
+      </c>
+      <c r="D938" t="n">
+        <v>4</v>
+      </c>
+      <c r="E938" t="n">
+        <v>4</v>
+      </c>
+      <c r="F938" t="n">
+        <v>4</v>
+      </c>
+      <c r="G938" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21946,6 +21946,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B939" t="n">
+        <v>0</v>
+      </c>
+      <c r="C939" t="n">
+        <v>4</v>
+      </c>
+      <c r="D939" t="n">
+        <v>4</v>
+      </c>
+      <c r="E939" t="n">
+        <v>4</v>
+      </c>
+      <c r="F939" t="n">
+        <v>4</v>
+      </c>
+      <c r="G939" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21810,7 +21810,7 @@
     </row>
     <row r="933">
       <c r="A933" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B933" t="n">
         <v>0</v>
@@ -21833,7 +21833,7 @@
     </row>
     <row r="934">
       <c r="A934" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B934" t="n">
         <v>0</v>
@@ -21856,7 +21856,7 @@
     </row>
     <row r="935">
       <c r="A935" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B935" t="n">
         <v>0</v>
@@ -21879,7 +21879,7 @@
     </row>
     <row r="936">
       <c r="A936" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B936" t="n">
         <v>0</v>
@@ -21902,7 +21902,7 @@
     </row>
     <row r="937">
       <c r="A937" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B937" t="n">
         <v>0</v>
@@ -21925,7 +21925,7 @@
     </row>
     <row r="938">
       <c r="A938" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B938" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     </row>
     <row r="939">
       <c r="A939" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B939" t="n">
         <v>0</v>
@@ -21966,6 +21966,29 @@
         <v>4</v>
       </c>
       <c r="G939" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B940" t="n">
+        <v>0</v>
+      </c>
+      <c r="C940" t="n">
+        <v>4</v>
+      </c>
+      <c r="D940" t="n">
+        <v>4</v>
+      </c>
+      <c r="E940" t="n">
+        <v>4</v>
+      </c>
+      <c r="F940" t="n">
+        <v>4</v>
+      </c>
+      <c r="G940" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -21992,6 +21992,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B941" t="n">
+        <v>0</v>
+      </c>
+      <c r="C941" t="n">
+        <v>4</v>
+      </c>
+      <c r="D941" t="n">
+        <v>4</v>
+      </c>
+      <c r="E941" t="n">
+        <v>4</v>
+      </c>
+      <c r="F941" t="n">
+        <v>4</v>
+      </c>
+      <c r="G941" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B942" t="n">
+        <v>0</v>
+      </c>
+      <c r="C942" t="n">
+        <v>4</v>
+      </c>
+      <c r="D942" t="n">
+        <v>4</v>
+      </c>
+      <c r="E942" t="n">
+        <v>4</v>
+      </c>
+      <c r="F942" t="n">
+        <v>4</v>
+      </c>
+      <c r="G942" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22038,6 +22038,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B943" t="n">
+        <v>0</v>
+      </c>
+      <c r="C943" t="n">
+        <v>4</v>
+      </c>
+      <c r="D943" t="n">
+        <v>4</v>
+      </c>
+      <c r="E943" t="n">
+        <v>4</v>
+      </c>
+      <c r="F943" t="n">
+        <v>4</v>
+      </c>
+      <c r="G943" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22061,6 +22061,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B944" t="n">
+        <v>0</v>
+      </c>
+      <c r="C944" t="n">
+        <v>4</v>
+      </c>
+      <c r="D944" t="n">
+        <v>4</v>
+      </c>
+      <c r="E944" t="n">
+        <v>4</v>
+      </c>
+      <c r="F944" t="n">
+        <v>4</v>
+      </c>
+      <c r="G944" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22084,6 +22084,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B945" t="n">
+        <v>0</v>
+      </c>
+      <c r="C945" t="n">
+        <v>4</v>
+      </c>
+      <c r="D945" t="n">
+        <v>4</v>
+      </c>
+      <c r="E945" t="n">
+        <v>4</v>
+      </c>
+      <c r="F945" t="n">
+        <v>4</v>
+      </c>
+      <c r="G945" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22107,6 +22107,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B946" t="n">
+        <v>0</v>
+      </c>
+      <c r="C946" t="n">
+        <v>4</v>
+      </c>
+      <c r="D946" t="n">
+        <v>4</v>
+      </c>
+      <c r="E946" t="n">
+        <v>4</v>
+      </c>
+      <c r="F946" t="n">
+        <v>4</v>
+      </c>
+      <c r="G946" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22130,6 +22130,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B947" t="n">
+        <v>0</v>
+      </c>
+      <c r="C947" t="n">
+        <v>4</v>
+      </c>
+      <c r="D947" t="n">
+        <v>4</v>
+      </c>
+      <c r="E947" t="n">
+        <v>4</v>
+      </c>
+      <c r="F947" t="n">
+        <v>4</v>
+      </c>
+      <c r="G947" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22153,6 +22153,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B948" t="n">
+        <v>0</v>
+      </c>
+      <c r="C948" t="n">
+        <v>4</v>
+      </c>
+      <c r="D948" t="n">
+        <v>4</v>
+      </c>
+      <c r="E948" t="n">
+        <v>4</v>
+      </c>
+      <c r="F948" t="n">
+        <v>4</v>
+      </c>
+      <c r="G948" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22176,6 +22176,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B949" t="n">
+        <v>0</v>
+      </c>
+      <c r="C949" t="n">
+        <v>4</v>
+      </c>
+      <c r="D949" t="n">
+        <v>4</v>
+      </c>
+      <c r="E949" t="n">
+        <v>4</v>
+      </c>
+      <c r="F949" t="n">
+        <v>4</v>
+      </c>
+      <c r="G949" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22199,6 +22199,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B950" t="n">
+        <v>0</v>
+      </c>
+      <c r="C950" t="n">
+        <v>4</v>
+      </c>
+      <c r="D950" t="n">
+        <v>4</v>
+      </c>
+      <c r="E950" t="n">
+        <v>4</v>
+      </c>
+      <c r="F950" t="n">
+        <v>4</v>
+      </c>
+      <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22222,6 +22222,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B951" t="n">
+        <v>0</v>
+      </c>
+      <c r="C951" t="n">
+        <v>4</v>
+      </c>
+      <c r="D951" t="n">
+        <v>4</v>
+      </c>
+      <c r="E951" t="n">
+        <v>4</v>
+      </c>
+      <c r="F951" t="n">
+        <v>4</v>
+      </c>
+      <c r="G951" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22245,6 +22245,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B952" t="n">
+        <v>0</v>
+      </c>
+      <c r="C952" t="n">
+        <v>4</v>
+      </c>
+      <c r="D952" t="n">
+        <v>4</v>
+      </c>
+      <c r="E952" t="n">
+        <v>4</v>
+      </c>
+      <c r="F952" t="n">
+        <v>4</v>
+      </c>
+      <c r="G952" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22268,6 +22268,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B953" t="n">
+        <v>0</v>
+      </c>
+      <c r="C953" t="n">
+        <v>4</v>
+      </c>
+      <c r="D953" t="n">
+        <v>4</v>
+      </c>
+      <c r="E953" t="n">
+        <v>4</v>
+      </c>
+      <c r="F953" t="n">
+        <v>4</v>
+      </c>
+      <c r="G953" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22291,6 +22291,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B954" t="n">
+        <v>0</v>
+      </c>
+      <c r="C954" t="n">
+        <v>4</v>
+      </c>
+      <c r="D954" t="n">
+        <v>4</v>
+      </c>
+      <c r="E954" t="n">
+        <v>4</v>
+      </c>
+      <c r="F954" t="n">
+        <v>4</v>
+      </c>
+      <c r="G954" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22314,6 +22314,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B955" t="n">
+        <v>0</v>
+      </c>
+      <c r="C955" t="n">
+        <v>4</v>
+      </c>
+      <c r="D955" t="n">
+        <v>4</v>
+      </c>
+      <c r="E955" t="n">
+        <v>4</v>
+      </c>
+      <c r="F955" t="n">
+        <v>4</v>
+      </c>
+      <c r="G955" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22337,6 +22337,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B956" t="n">
+        <v>0</v>
+      </c>
+      <c r="C956" t="n">
+        <v>4</v>
+      </c>
+      <c r="D956" t="n">
+        <v>4</v>
+      </c>
+      <c r="E956" t="n">
+        <v>4</v>
+      </c>
+      <c r="F956" t="n">
+        <v>4</v>
+      </c>
+      <c r="G956" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22383,6 +22383,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B958" t="n">
+        <v>0</v>
+      </c>
+      <c r="C958" t="n">
+        <v>4</v>
+      </c>
+      <c r="D958" t="n">
+        <v>4</v>
+      </c>
+      <c r="E958" t="n">
+        <v>4</v>
+      </c>
+      <c r="F958" t="n">
+        <v>4</v>
+      </c>
+      <c r="G958" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22406,6 +22406,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B959" t="n">
+        <v>0</v>
+      </c>
+      <c r="C959" t="n">
+        <v>4</v>
+      </c>
+      <c r="D959" t="n">
+        <v>4</v>
+      </c>
+      <c r="E959" t="n">
+        <v>4</v>
+      </c>
+      <c r="F959" t="n">
+        <v>4</v>
+      </c>
+      <c r="G959" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22429,6 +22429,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B960" t="n">
+        <v>0</v>
+      </c>
+      <c r="C960" t="n">
+        <v>4</v>
+      </c>
+      <c r="D960" t="n">
+        <v>4</v>
+      </c>
+      <c r="E960" t="n">
+        <v>4</v>
+      </c>
+      <c r="F960" t="n">
+        <v>4</v>
+      </c>
+      <c r="G960" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -22452,6 +22452,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B961" t="n">
+        <v>0</v>
+      </c>
+      <c r="C961" t="n">
+        <v>4</v>
+      </c>
+      <c r="D961" t="n">
+        <v>4</v>
+      </c>
+      <c r="E961" t="n">
+        <v>4</v>
+      </c>
+      <c r="F961" t="n">
+        <v>4</v>
+      </c>
+      <c r="G961" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28276,6 +28276,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" t="s">
+        <v>9</v>
+      </c>
+      <c r="B963" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C963" t="n">
+        <v>4</v>
+      </c>
+      <c r="D963" t="n">
+        <v>4</v>
+      </c>
+      <c r="E963" t="n">
+        <v>4</v>
+      </c>
+      <c r="F963" t="n">
+        <v>4</v>
+      </c>
+      <c r="G963" t="n">
+        <v>4</v>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+      <c r="I963" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28305,6 +28305,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="s">
+        <v>9</v>
+      </c>
+      <c r="B964" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C964" t="n">
+        <v>4</v>
+      </c>
+      <c r="D964" t="n">
+        <v>4</v>
+      </c>
+      <c r="E964" t="n">
+        <v>4</v>
+      </c>
+      <c r="F964" t="n">
+        <v>4</v>
+      </c>
+      <c r="G964" t="n">
+        <v>4</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28334,6 +28334,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" t="s">
+        <v>9</v>
+      </c>
+      <c r="B965" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C965" t="n">
+        <v>4</v>
+      </c>
+      <c r="D965" t="n">
+        <v>4</v>
+      </c>
+      <c r="E965" t="n">
+        <v>4</v>
+      </c>
+      <c r="F965" t="n">
+        <v>4</v>
+      </c>
+      <c r="G965" t="n">
+        <v>4</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28363,6 +28363,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="s">
+        <v>9</v>
+      </c>
+      <c r="B966" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C966" t="n">
+        <v>4</v>
+      </c>
+      <c r="D966" t="n">
+        <v>4</v>
+      </c>
+      <c r="E966" t="n">
+        <v>4</v>
+      </c>
+      <c r="F966" t="n">
+        <v>4</v>
+      </c>
+      <c r="G966" t="n">
+        <v>4</v>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28392,6 +28392,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" t="s">
+        <v>9</v>
+      </c>
+      <c r="B967" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C967" t="n">
+        <v>4</v>
+      </c>
+      <c r="D967" t="n">
+        <v>4</v>
+      </c>
+      <c r="E967" t="n">
+        <v>4</v>
+      </c>
+      <c r="F967" t="n">
+        <v>4</v>
+      </c>
+      <c r="G967" t="n">
+        <v>4</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28421,6 +28421,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="s">
+        <v>9</v>
+      </c>
+      <c r="B968" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C968" t="n">
+        <v>4</v>
+      </c>
+      <c r="D968" t="n">
+        <v>4</v>
+      </c>
+      <c r="E968" t="n">
+        <v>4</v>
+      </c>
+      <c r="F968" t="n">
+        <v>4</v>
+      </c>
+      <c r="G968" t="n">
+        <v>4</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28450,6 +28450,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="s">
+        <v>9</v>
+      </c>
+      <c r="B969" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C969" t="n">
+        <v>4</v>
+      </c>
+      <c r="D969" t="n">
+        <v>4</v>
+      </c>
+      <c r="E969" t="n">
+        <v>4</v>
+      </c>
+      <c r="F969" t="n">
+        <v>4</v>
+      </c>
+      <c r="G969" t="n">
+        <v>4</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28479,6 +28479,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="s">
+        <v>9</v>
+      </c>
+      <c r="B970" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C970" t="n">
+        <v>4</v>
+      </c>
+      <c r="D970" t="n">
+        <v>4</v>
+      </c>
+      <c r="E970" t="n">
+        <v>4</v>
+      </c>
+      <c r="F970" t="n">
+        <v>4</v>
+      </c>
+      <c r="G970" t="n">
+        <v>4</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I970" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOT.MI.xlsx
+++ b/data/DOT.MI.xlsx
@@ -28508,6 +28508,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="s">
+        <v>9</v>
+      </c>
+      <c r="B971" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C971" t="n">
+        <v>4</v>
+      </c>
+      <c r="D971" t="n">
+        <v>4</v>
+      </c>
+      <c r="E971" t="n">
+        <v>4</v>
+      </c>
+      <c r="F971" t="n">
+        <v>4</v>
+      </c>
+      <c r="G971" t="n">
+        <v>4</v>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
